--- a/data/trans_dic/P38A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,77; 92,75</t>
+          <t>88,85; 92,64</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,51; 91,91</t>
+          <t>87,44; 91,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,67; 92,65</t>
+          <t>87,69; 92,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,84; 95,47</t>
+          <t>92,82; 95,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,96; 95,96</t>
+          <t>92,8; 95,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,34; 95,77</t>
+          <t>92,3; 95,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,65; 93,82</t>
+          <t>91,57; 93,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,04; 93,6</t>
+          <t>91,33; 93,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,24; 94,19</t>
+          <t>91,08; 94,0</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,7; 83,05</t>
+          <t>79,42; 83,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,24; 82,59</t>
+          <t>79,39; 82,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>50,42; 81,12</t>
+          <t>48,66; 81,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,59; 87,93</t>
+          <t>84,57; 87,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,18; 89,22</t>
+          <t>86,33; 89,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,63; 89,46</t>
+          <t>76,53; 89,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,55; 84,95</t>
+          <t>82,38; 84,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,16; 85,44</t>
+          <t>83,14; 85,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>66,55; 84,46</t>
+          <t>62,95; 83,96</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,83; 92,4</t>
+          <t>86,71; 92,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>80,83; 87,42</t>
+          <t>81,1; 87,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,93; 90,88</t>
+          <t>83,72; 90,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,74; 92,05</t>
+          <t>86,01; 91,96</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>84,98; 90,7</t>
+          <t>85,15; 90,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>88,06; 92,6</t>
+          <t>87,58; 92,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,44; 91,6</t>
+          <t>87,26; 91,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,91; 88,17</t>
+          <t>83,93; 88,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,64; 90,84</t>
+          <t>86,85; 91,1</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,03; 86,57</t>
+          <t>84,02; 86,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,31; 84,78</t>
+          <t>82,24; 84,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,38; 84,18</t>
+          <t>60,24; 84,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,49; 90,6</t>
+          <t>88,62; 90,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,74; 90,87</t>
+          <t>88,8; 90,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,3; 90,72</t>
+          <t>82,55; 90,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,63; 88,27</t>
+          <t>86,67; 88,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,91; 87,67</t>
+          <t>85,98; 87,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,11; 86,79</t>
+          <t>72,34; 86,77</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a</t>
+          <t>Población a la que le han tomado la tensión alguna vez un/a profesional sanitario/a (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>856837; 895275</t>
+          <t>857647; 894147</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>658366; 691431</t>
+          <t>657793; 690849</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>451457; 477109</t>
+          <t>451569; 477948</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1236451; 1271537</t>
+          <t>1236238; 1271127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>923849; 953668</t>
+          <t>922203; 951568</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>697642; 723544</t>
+          <t>697350; 722940</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2105341; 2155124</t>
+          <t>2103354; 2155939</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1589636; 1634416</t>
+          <t>1594783; 1637830</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1159142; 1196653</t>
+          <t>1157159; 1194260</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1557923; 1623488</t>
+          <t>1552519; 1623936</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1630507; 1699282</t>
+          <t>1633588; 1701571</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1154735; 1858028</t>
+          <t>1114430; 1856171</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1481357; 1539815</t>
+          <t>1480981; 1538677</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1707476; 1767837</t>
+          <t>1710524; 1768709</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1692553; 2002056</t>
+          <t>1712583; 2004405</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3059409; 3148087</t>
+          <t>3052824; 3145418</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3358800; 3450744</t>
+          <t>3358015; 3450351</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3013496; 3824450</t>
+          <t>2850429; 3801747</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>414419; 440986</t>
+          <t>413844; 441228</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>438967; 474758</t>
+          <t>440418; 475014</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536223; 587642</t>
+          <t>541335; 586839</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>392316; 421222</t>
+          <t>393576; 420805</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>464907; 496212</t>
+          <t>465838; 495896</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>581596; 611592</t>
+          <t>578419; 609301</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>817424; 856362</t>
+          <t>815746; 855154</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>914737; 961242</t>
+          <t>915037; 962840</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1132507; 1187338</t>
+          <t>1135257; 1190708</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2854803; 2941079</t>
+          <t>2854294; 2938256</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2759826; 2842621</t>
+          <t>2757604; 2843910</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2084265; 2905743</t>
+          <t>2079259; 2901539</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3133281; 3207939</t>
+          <t>3137616; 3211271</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3125465; 3200499</t>
+          <t>3127826; 3199148</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3006985; 3314738</t>
+          <t>3016136; 3305769</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6009993; 6124390</t>
+          <t>6013083; 6121024</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5906289; 6027559</t>
+          <t>5911479; 6020109</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5123869; 6167164</t>
+          <t>5139962; 6165945</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38A-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P38A-Estudios-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>91,67%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>88,85; 92,64</t>
+          <t>88,83; 92,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>87,44; 91,83</t>
+          <t>87,3; 91,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87,69; 92,82</t>
+          <t>84,98; 91,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,82; 95,44</t>
+          <t>92,67; 95,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>92,8; 95,75</t>
+          <t>92,86; 95,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,3; 95,69</t>
+          <t>92,46; 95,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,57; 93,85</t>
+          <t>91,56; 93,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91,33; 93,8</t>
+          <t>91,13; 93,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,08; 94,0</t>
+          <t>89,82; 93,09</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>79,42; 83,08</t>
+          <t>79,57; 83,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,39; 82,7</t>
+          <t>79,26; 82,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48,66; 81,04</t>
+          <t>76,95; 81,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>84,57; 87,86</t>
+          <t>84,57; 87,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,33; 89,27</t>
+          <t>86,49; 89,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>76,53; 89,57</t>
+          <t>84,03; 87,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,38; 84,87</t>
+          <t>82,37; 84,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>83,14; 85,43</t>
+          <t>83,22; 85,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62,95; 83,96</t>
+          <t>81,21; 83,99</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,71; 92,45</t>
+          <t>86,67; 92,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81,1; 87,47</t>
+          <t>80,98; 87,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>83,72; 90,75</t>
+          <t>85,74; 91,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,01; 91,96</t>
+          <t>85,87; 91,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>85,15; 90,64</t>
+          <t>85,19; 90,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,58; 92,25</t>
+          <t>87,89; 92,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,26; 91,48</t>
+          <t>87,16; 91,4</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>83,93; 88,32</t>
+          <t>83,88; 88,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,85; 91,1</t>
+          <t>87,51; 91,07</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -1008,32 +1008,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,02; 86,49</t>
+          <t>83,98; 86,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>82,24; 84,82</t>
+          <t>82,23; 84,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,24; 84,06</t>
+          <t>80,98; 84,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,62; 90,7</t>
+          <t>88,55; 90,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,8; 90,83</t>
+          <t>88,68; 90,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,55; 90,47</t>
+          <t>87,32; 89,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>85,98; 87,56</t>
+          <t>85,91; 87,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,34; 86,77</t>
+          <t>84,69; 86,77</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466061</t>
+          <t>510394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>712287</t>
+          <t>773490</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1178348</t>
+          <t>1283883</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>857647; 894147</t>
+          <t>857417; 894820</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>657793; 690849</t>
+          <t>656740; 689825</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>451569; 477948</t>
+          <t>491659; 526507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1236238; 1271127</t>
+          <t>1234301; 1267855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>922203; 951568</t>
+          <t>922834; 953307</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>697350; 722940</t>
+          <t>760036; 784821</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2103354; 2155939</t>
+          <t>2103224; 2155545</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1594783; 1637830</t>
+          <t>1591213; 1634666</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1157159; 1194260</t>
+          <t>1257971; 1303841</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1645547</t>
+          <t>1772983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1915741</t>
+          <t>1861470</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3561287</t>
+          <t>3634454</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1552519; 1623936</t>
+          <t>1555502; 1624967</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1633588; 1701571</t>
+          <t>1630901; 1701597</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1114430; 1856171</t>
+          <t>1716329; 1820268</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1480981; 1538677</t>
+          <t>1480918; 1537837</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1710524; 1768709</t>
+          <t>1713689; 1769928</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1712583; 2004405</t>
+          <t>1824608; 1896225</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3052824; 3145418</t>
+          <t>3052449; 3147108</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3358015; 3450351</t>
+          <t>3360993; 3454418</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2850429; 3801747</t>
+          <t>3574863; 3697392</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>569022</t>
+          <t>629503</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>596392</t>
+          <t>664239</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1165414</t>
+          <t>1293742</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>413844; 441228</t>
+          <t>413649; 441165</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>440418; 475014</t>
+          <t>439815; 474505</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>541335; 586839</t>
+          <t>610148; 647779</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>393576; 420805</t>
+          <t>392947; 420636</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>465838; 495896</t>
+          <t>466075; 496318</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>578419; 609301</t>
+          <t>645885; 678640</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>815746; 855154</t>
+          <t>814810; 854437</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>915037; 962840</t>
+          <t>914466; 961822</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1135257; 1190708</t>
+          <t>1265833; 1317238</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2680630</t>
+          <t>2912880</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3224420</t>
+          <t>3299199</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5905050</t>
+          <t>6212079</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2854294; 2938256</t>
+          <t>2853088; 2938685</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2757604; 2843910</t>
+          <t>2757205; 2841292</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2079259; 2901539</t>
+          <t>2850974; 2966618</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3137616; 3211271</t>
+          <t>3135086; 3207955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3127826; 3199148</t>
+          <t>3123335; 3199639</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3016136; 3305769</t>
+          <t>3255421; 3337732</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>6013083; 6121024</t>
+          <t>6013184; 6121196</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5911479; 6020109</t>
+          <t>5906690; 6018075</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>5139962; 6165945</t>
+          <t>6139300; 6290157</t>
         </is>
       </c>
     </row>
